--- a/invoices/invoice_2026-09-12.xlsx
+++ b/invoices/invoice_2026-09-12.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>CV SOLUSI DIGITAL Nusantara</t>
+          <t>UD BERKAH JAYA</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>Jl. Pemuda No. 55, Surabaya 60271</t>
+          <t>Jl. Raya Bogor No. 88, Depok 16413</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Andi Wijaya | andi@solusid.co.id</t>
+          <t>Hendra Putra | hendra@berkahjaya.id</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
     <row r="16" ht="28" customHeight="1">
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>API Development</t>
+          <t>Data Analysis &amp; Reporting</t>
         </is>
       </c>
       <c r="C16" s="12" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D16" s="13" t="n">
-        <v>900000</v>
+        <v>600000</v>
       </c>
       <c r="E16" s="14" t="n">
         <v>0.11</v>
@@ -714,14 +714,14 @@
     <row r="17" ht="28" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Technical Documentation</t>
+          <t>Cloud Infrastructure Setup</t>
         </is>
       </c>
       <c r="C17" s="12" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="D17" s="13" t="n">
-        <v>250000</v>
+        <v>1200000</v>
       </c>
       <c r="E17" s="14" t="n">
         <v>0.11</v>
